--- a/data/xlsx/mahila-polytechnic--bakery-and-food-production-advanced.xlsx
+++ b/data/xlsx/mahila-polytechnic--bakery-and-food-production-advanced.xlsx
@@ -645,7 +645,9 @@
       <c r="C16" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="9" t="n"/>
+      <c r="D16" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E16" s="9" t="n">
         <v>5</v>
       </c>
@@ -667,7 +669,9 @@
       <c r="C17" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E17" s="9" t="n">
         <v>5</v>
       </c>
@@ -689,7 +693,9 @@
       <c r="C18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="9" t="n"/>
+      <c r="D18" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E18" s="9" t="n">
         <v>5</v>
       </c>
@@ -711,7 +717,9 @@
       <c r="C19" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D19" s="9" t="n"/>
+      <c r="D19" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E19" s="9" t="n">
         <v>5</v>
       </c>
@@ -733,7 +741,9 @@
       <c r="C20" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="9" t="n"/>
+      <c r="D20" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E20" s="9" t="n">
         <v>5</v>
       </c>
@@ -755,7 +765,9 @@
       <c r="C21" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="9" t="n"/>
+      <c r="D21" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E21" s="9" t="n">
         <v>4</v>
       </c>
@@ -777,7 +789,9 @@
       <c r="C22" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D22" s="9" t="n"/>
+      <c r="D22" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E22" s="9" t="n">
         <v>9</v>
       </c>
@@ -799,7 +813,9 @@
       <c r="C23" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D23" s="9" t="n"/>
+      <c r="D23" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E23" s="9" t="n">
         <v>9</v>
       </c>
@@ -821,7 +837,9 @@
       <c r="C24" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D24" s="9" t="n"/>
+      <c r="D24" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E24" s="9" t="n">
         <v>9</v>
       </c>
@@ -843,7 +861,9 @@
       <c r="C25" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="9" t="n"/>
+      <c r="D25" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E25" s="9" t="n">
         <v>8</v>
       </c>
@@ -865,7 +885,9 @@
       <c r="C26" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="9" t="n"/>
+      <c r="D26" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E26" s="9" t="n">
         <v>8</v>
       </c>
@@ -887,7 +909,9 @@
       <c r="C27" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D27" s="9" t="n"/>
+      <c r="D27" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="9" t="n">
         <v>8</v>
       </c>
@@ -909,7 +933,9 @@
       <c r="C28" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E28" s="9" t="n">
         <v>7</v>
       </c>
@@ -931,7 +957,9 @@
       <c r="C29" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E29" s="9" t="n">
         <v>6</v>
       </c>
@@ -953,7 +981,9 @@
       <c r="C30" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D30" s="9" t="n"/>
+      <c r="D30" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E30" s="9" t="n">
         <v>6</v>
       </c>
@@ -975,7 +1005,9 @@
       <c r="C31" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D31" s="9" t="n"/>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E31" s="9" t="n">
         <v>4</v>
       </c>
@@ -997,7 +1029,9 @@
       <c r="C32" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D32" s="9" t="n"/>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E32" s="9" t="n">
         <v>3</v>
       </c>
@@ -1023,7 +1057,9 @@
       <c r="C33" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="D33" s="9" t="n"/>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E33" s="9" t="n">
         <v>3</v>
       </c>
@@ -1045,7 +1081,9 @@
       <c r="C34" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D34" s="9" t="n"/>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="9" t="n">
         <v>4</v>
       </c>
@@ -1067,7 +1105,9 @@
       <c r="C35" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="D35" s="9" t="n"/>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="9" t="n">
         <v>4</v>
       </c>
@@ -1089,7 +1129,9 @@
       <c r="C36" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="D36" s="9" t="n"/>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="9" t="n">
         <v>6</v>
       </c>
@@ -1111,7 +1153,9 @@
       <c r="C37" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="D37" s="9" t="n"/>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="9" t="n">
         <v>7</v>
       </c>
@@ -1133,7 +1177,9 @@
       <c r="C38" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="D38" s="9" t="n"/>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="9" t="n">
         <v>6</v>
       </c>
@@ -1155,7 +1201,9 @@
       <c r="C39" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="D39" s="9" t="n"/>
+      <c r="D39" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E39" s="9" t="n">
         <v>4</v>
       </c>
@@ -1177,7 +1225,9 @@
       <c r="C40" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="D40" s="9" t="n"/>
+      <c r="D40" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E40" s="9" t="n">
         <v>5</v>
       </c>
@@ -1197,7 +1247,9 @@
         </is>
       </c>
       <c r="C41" s="9" t="n"/>
-      <c r="D41" s="9" t="n"/>
+      <c r="D41" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="E41" s="9" t="n">
         <v>3</v>
       </c>
